--- a/tools/memory_map/AST2700A2_OTP_memory_map.xlsx
+++ b/tools/memory_map/AST2700A2_OTP_memory_map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jheng-shuo_lin\Desktop\OTP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9642C3E1-A1F7-4849-B1E8-F222A8F19E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAE92357-9BBF-4466-BF2A-457B28F06D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{40652B66-A45B-48BE-91E6-4A13E915CABA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="10" xr2:uid="{40652B66-A45B-48BE-91E6-4A13E915CABA}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="6" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1480" uniqueCount="754">
   <si>
     <t>High Level overview of OTP memory layout</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1540,9 +1540,6 @@
   <si>
     <t>DBG</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Static protect</t>
   </si>
   <si>
     <t>OTPSTRAP_EXT</t>
@@ -3109,6 +3106,18 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>HW Static protect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recovery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROM-stage static protect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>1. Removed OTPCFG2[14] dis_cptra_owner_key_retry; OTPCFG2[15:14] is now reserved.
 2. Changed OTPUSR2 (0x6C0–0x7FF) from customer-reserved space to a ROM patch region, expanding the ROM patch range to 0x6C0–0xFFF.
 3. Added the following fields to ASPEED provisioning:
@@ -3128,11 +3137,11 @@
 8. Corrected typographical errors caused by an unintended replacement of "to" with "of" across multiple worksheets.
 9. Added the missing OTPCAL Reserved fields at 0x1C00[15:1] and 0x1C01[15:1].
 10. Corrected the Caliptra Runtime Hardware SVN policy description
-    from "FMC SVN &gt;= HW FMC SVN" to
-    "RUNTIME SVN &gt;= HW RUNTIME SVN".
+    from "FMC SVN &gt;= HW FMC SVN" to "RUNTIME SVN &gt;= HW RUNTIME SVN".
 11. Corrected the following OTPSTRAP_EXT bit field definitions:
     a. OTPSTRAP_EXT1 udbg_to_sel from 11:10:00 to 11:10.
-    b. OTPSTRAP_EXT7 Reserved from bit 15 to bits 15:0.</t>
+    b. OTPSTRAP_EXT7 Reserved from bit 15 to bits 15:0.
+12. Updated the Static Protect descriptions in the OTPCFG Note column to distinguish between HW Static Protect and ROM-stage Static Protect.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3882,7 +3891,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="180">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4413,15 +4422,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4971,7 +4971,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="123" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -5010,21 +5010,21 @@
       <c r="A5" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="177">
+      <c r="B5" s="117">
         <v>0</v>
       </c>
-      <c r="C5" s="177" t="str">
+      <c r="C5" s="117" t="str">
         <f>DEC2HEX(HEX2DEC(B6)-1)</f>
         <v>3DF</v>
       </c>
-      <c r="D5" s="177">
+      <c r="D5" s="117">
         <f>F5/2</f>
         <v>992</v>
       </c>
-      <c r="E5" s="177">
+      <c r="E5" s="117">
         <v>15872</v>
       </c>
-      <c r="F5" s="177">
+      <c r="F5" s="117">
         <f>E5/8</f>
         <v>1984</v>
       </c>
@@ -5033,22 +5033,22 @@
       <c r="A6" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="177" t="str">
+      <c r="B6" s="117" t="str">
         <f>DEC2HEX(HEX2DEC(B5)+D5)</f>
         <v>3E0</v>
       </c>
-      <c r="C6" s="177" t="str">
+      <c r="C6" s="117" t="str">
         <f t="shared" ref="C6" si="0">DEC2HEX(HEX2DEC(B7)-1)</f>
         <v>3FF</v>
       </c>
-      <c r="D6" s="177">
+      <c r="D6" s="117">
         <f t="shared" ref="D6" si="1">F6/2</f>
         <v>32</v>
       </c>
-      <c r="E6" s="177">
+      <c r="E6" s="117">
         <v>512</v>
       </c>
-      <c r="F6" s="177">
+      <c r="F6" s="117">
         <f t="shared" ref="F6:F13" si="2">E6/8</f>
         <v>64</v>
       </c>
@@ -5057,22 +5057,22 @@
       <c r="A7" s="125" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="177" t="str">
+      <c r="B7" s="117" t="str">
         <f>DEC2HEX(HEX2DEC(B6)+D6)</f>
         <v>400</v>
       </c>
-      <c r="C7" s="177" t="str">
+      <c r="C7" s="117" t="str">
         <f t="shared" ref="C7:C13" si="3">DEC2HEX(HEX2DEC(B8)-1)</f>
         <v>41F</v>
       </c>
-      <c r="D7" s="177">
+      <c r="D7" s="117">
         <f t="shared" ref="D7:D13" si="4">F7/2</f>
         <v>32</v>
       </c>
-      <c r="E7" s="177">
+      <c r="E7" s="117">
         <v>512</v>
       </c>
-      <c r="F7" s="177">
+      <c r="F7" s="117">
         <f t="shared" si="2"/>
         <v>64</v>
       </c>
@@ -5081,46 +5081,46 @@
       <c r="A8" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="177" t="str">
+      <c r="B8" s="117" t="str">
         <f t="shared" ref="B8:B14" si="5">DEC2HEX(HEX2DEC(B7)+D7)</f>
         <v>420</v>
       </c>
-      <c r="C8" s="177" t="str">
+      <c r="C8" s="117" t="str">
         <f t="shared" si="3"/>
         <v>42F</v>
       </c>
-      <c r="D8" s="177">
+      <c r="D8" s="117">
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="E8" s="177">
+      <c r="E8" s="117">
         <v>256</v>
       </c>
-      <c r="F8" s="177">
+      <c r="F8" s="117">
         <f t="shared" si="2"/>
         <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="125" t="s">
-        <v>394</v>
-      </c>
-      <c r="B9" s="177" t="str">
+        <v>393</v>
+      </c>
+      <c r="B9" s="117" t="str">
         <f t="shared" si="5"/>
         <v>430</v>
       </c>
-      <c r="C9" s="177" t="str">
+      <c r="C9" s="117" t="str">
         <f t="shared" si="3"/>
         <v>43F</v>
       </c>
-      <c r="D9" s="177">
+      <c r="D9" s="117">
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="E9" s="177">
+      <c r="E9" s="117">
         <v>256</v>
       </c>
-      <c r="F9" s="177">
+      <c r="F9" s="117">
         <f t="shared" si="2"/>
         <v>32</v>
       </c>
@@ -5129,22 +5129,22 @@
       <c r="A10" s="125" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="177" t="str">
+      <c r="B10" s="117" t="str">
         <f t="shared" si="5"/>
         <v>440</v>
       </c>
-      <c r="C10" s="177" t="str">
+      <c r="C10" s="117" t="str">
         <f t="shared" si="3"/>
         <v>FFF</v>
       </c>
-      <c r="D10" s="177">
+      <c r="D10" s="117">
         <f t="shared" si="4"/>
         <v>3008</v>
       </c>
-      <c r="E10" s="177">
+      <c r="E10" s="117">
         <v>48128</v>
       </c>
-      <c r="F10" s="177">
+      <c r="F10" s="117">
         <f t="shared" si="2"/>
         <v>6016</v>
       </c>
@@ -5153,22 +5153,22 @@
       <c r="A11" s="125" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="177" t="str">
+      <c r="B11" s="117" t="str">
         <f t="shared" si="5"/>
         <v>1000</v>
       </c>
-      <c r="C11" s="177" t="str">
+      <c r="C11" s="117" t="str">
         <f t="shared" si="3"/>
         <v>1BFF</v>
       </c>
-      <c r="D11" s="177">
+      <c r="D11" s="117">
         <f t="shared" si="4"/>
         <v>3072</v>
       </c>
-      <c r="E11" s="177">
+      <c r="E11" s="117">
         <v>49152</v>
       </c>
-      <c r="F11" s="177">
+      <c r="F11" s="117">
         <f t="shared" si="2"/>
         <v>6144</v>
       </c>
@@ -5177,22 +5177,22 @@
       <c r="A12" s="125" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="177" t="str">
+      <c r="B12" s="117" t="str">
         <f t="shared" si="5"/>
         <v>1C00</v>
       </c>
-      <c r="C12" s="177" t="str">
+      <c r="C12" s="117" t="str">
         <f t="shared" si="3"/>
         <v>1F7F</v>
       </c>
-      <c r="D12" s="177">
+      <c r="D12" s="117">
         <f t="shared" si="4"/>
         <v>896</v>
       </c>
-      <c r="E12" s="177">
+      <c r="E12" s="117">
         <v>14336</v>
       </c>
-      <c r="F12" s="177">
+      <c r="F12" s="117">
         <f t="shared" si="2"/>
         <v>1792</v>
       </c>
@@ -5201,22 +5201,22 @@
       <c r="A13" s="126" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="178" t="str">
+      <c r="B13" s="119" t="str">
         <f t="shared" si="5"/>
         <v>1F80</v>
       </c>
-      <c r="C13" s="178" t="str">
+      <c r="C13" s="119" t="str">
         <f t="shared" si="3"/>
         <v>1FFF</v>
       </c>
-      <c r="D13" s="178">
+      <c r="D13" s="119">
         <f t="shared" si="4"/>
         <v>128</v>
       </c>
-      <c r="E13" s="178">
+      <c r="E13" s="119">
         <v>2048</v>
       </c>
-      <c r="F13" s="178">
+      <c r="F13" s="119">
         <f t="shared" si="2"/>
         <v>256</v>
       </c>
@@ -5225,20 +5225,20 @@
       <c r="A14" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="179" t="str">
+      <c r="B14" s="137" t="str">
         <f t="shared" si="5"/>
         <v>2000</v>
       </c>
-      <c r="C14" s="179"/>
-      <c r="D14" s="179">
+      <c r="C14" s="137"/>
+      <c r="D14" s="137">
         <f>SUM(D5:D13)</f>
         <v>8192</v>
       </c>
-      <c r="E14" s="179">
+      <c r="E14" s="137">
         <f>SUM(E5:E13)</f>
         <v>131072</v>
       </c>
-      <c r="F14" s="179">
+      <c r="F14" s="137">
         <f>SUM(F5:F13)</f>
         <v>16384</v>
       </c>
@@ -5248,12 +5248,12 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="152" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="171" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B18" s="172"/>
       <c r="C18" s="172"/>
@@ -5307,7 +5307,7 @@
         <v>306</v>
       </c>
       <c r="B1" s="110" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C1" s="110" t="s">
         <v>308</v>
@@ -5336,7 +5336,7 @@
         <v>301</v>
       </c>
       <c r="C2" s="121" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D2" s="18">
         <v>512</v>
@@ -5350,7 +5350,7 @@
         <v>32</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2" s="18"/>
     </row>
@@ -5363,7 +5363,7 @@
         <v>302</v>
       </c>
       <c r="C3" s="121" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D3" s="18">
         <v>256</v>
@@ -5377,7 +5377,7 @@
         <v>16</v>
       </c>
       <c r="G3" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H3" s="18" t="s">
         <v>294</v>
@@ -5392,7 +5392,7 @@
         <v>302</v>
       </c>
       <c r="C4" s="121" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D4" s="18">
         <v>384</v>
@@ -5421,7 +5421,7 @@
         <v>302</v>
       </c>
       <c r="C5" s="121" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D5" s="18">
         <v>256</v>
@@ -5435,7 +5435,7 @@
         <v>16</v>
       </c>
       <c r="G5" s="54" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H5" s="18" t="s">
         <v>294</v>
@@ -5450,7 +5450,7 @@
         <v>302</v>
       </c>
       <c r="C6" s="121" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D6" s="18">
         <v>256</v>
@@ -5479,7 +5479,7 @@
         <v>302</v>
       </c>
       <c r="C7" s="121" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D7" s="18">
         <v>384</v>
@@ -5558,43 +5558,43 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.625" customWidth="1"/>
-    <col min="2" max="2" width="93.375" customWidth="1"/>
+    <col min="2" max="2" width="120.375" customWidth="1"/>
     <col min="3" max="3" width="38.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="174" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B1" s="175"/>
       <c r="C1" s="176"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="161" t="s">
+        <v>637</v>
+      </c>
+      <c r="B2" s="161" t="s">
         <v>638</v>
       </c>
-      <c r="B2" s="161" t="s">
+      <c r="C2" s="161" t="s">
         <v>639</v>
-      </c>
-      <c r="C2" s="161" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="166" t="s">
+        <v>739</v>
+      </c>
+      <c r="B3" s="167" t="s">
         <v>740</v>
       </c>
-      <c r="B3" s="167" t="s">
+      <c r="C3" s="167"/>
+    </row>
+    <row r="4" spans="1:3" ht="378" x14ac:dyDescent="0.25">
+      <c r="A4" s="169" t="s">
         <v>741</v>
       </c>
-      <c r="C3" s="167"/>
-    </row>
-    <row r="4" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="169" t="s">
-        <v>742</v>
-      </c>
       <c r="B4" s="168" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C4" s="168"/>
     </row>
@@ -5770,7 +5770,7 @@
         <v>306</v>
       </c>
       <c r="B1" s="110" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C1" s="110" t="s">
         <v>308</v>
@@ -5886,7 +5886,7 @@
         <v>3E3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C5" s="61" t="s">
         <v>311</v>
@@ -5903,7 +5903,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H5" s="18" t="s">
         <v>27</v>
@@ -5932,7 +5932,7 @@
         <v>4</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H6" s="20" t="s">
         <v>29</v>
@@ -5990,7 +5990,7 @@
         <v>8</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H8" s="20" t="s">
         <v>29</v>
@@ -6034,7 +6034,7 @@
         <v>25</v>
       </c>
       <c r="C10" s="61" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D10" s="16">
         <v>12</v>
@@ -6090,7 +6090,7 @@
         <v>25</v>
       </c>
       <c r="C12" s="94" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D12" s="16">
         <v>176</v>
@@ -6175,7 +6175,7 @@
     <col min="5" max="5" width="11.25" customWidth="1"/>
     <col min="6" max="6" width="11.875" customWidth="1"/>
     <col min="7" max="7" width="65.5" customWidth="1"/>
-    <col min="8" max="8" width="19.25" customWidth="1"/>
+    <col min="8" max="8" width="23.125" customWidth="1"/>
     <col min="9" max="9" width="20.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6184,7 +6184,7 @@
         <v>306</v>
       </c>
       <c r="B1" s="110" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C1" s="110" t="s">
         <v>308</v>
@@ -6264,7 +6264,7 @@
         <v>41</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>355</v>
+        <v>750</v>
       </c>
       <c r="I3" s="72" t="s">
         <v>319</v>
@@ -6292,7 +6292,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="34" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H4" s="16" t="s">
         <v>355</v>
@@ -6326,7 +6326,7 @@
         <v>44</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>355</v>
+        <v>750</v>
       </c>
       <c r="I5" s="72" t="s">
         <v>319</v>
@@ -6357,7 +6357,7 @@
         <v>46</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>355</v>
+        <v>750</v>
       </c>
       <c r="I6" s="72" t="s">
         <v>319</v>
@@ -6388,7 +6388,7 @@
         <v>48</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>355</v>
+        <v>750</v>
       </c>
       <c r="I7" s="72" t="s">
         <v>319</v>
@@ -6416,7 +6416,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="69" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H8" s="16" t="s">
         <v>355</v>
@@ -6430,7 +6430,7 @@
         <v>400</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C9" s="62">
         <v>8</v>
@@ -6447,7 +6447,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="70" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H9" s="16" t="s">
         <v>355</v>
@@ -6481,7 +6481,7 @@
         <v>51</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>355</v>
+        <v>750</v>
       </c>
       <c r="I10" s="72" t="s">
         <v>319</v>
@@ -6512,7 +6512,7 @@
         <v>53</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>355</v>
+        <v>750</v>
       </c>
       <c r="I11" s="72" t="s">
         <v>319</v>
@@ -6543,7 +6543,7 @@
         <v>55</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>355</v>
+        <v>750</v>
       </c>
       <c r="I12" s="72" t="s">
         <v>319</v>
@@ -6574,7 +6574,7 @@
         <v>57</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>355</v>
+        <v>750</v>
       </c>
       <c r="I13" s="72" t="s">
         <v>319</v>
@@ -6605,7 +6605,7 @@
         <v>59</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>355</v>
+        <v>750</v>
       </c>
       <c r="I14" s="72" t="s">
         <v>319</v>
@@ -6636,7 +6636,7 @@
         <v>61</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>355</v>
+        <v>750</v>
       </c>
       <c r="I15" s="72" t="s">
         <v>319</v>
@@ -6667,7 +6667,7 @@
         <v>63</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>355</v>
+        <v>750</v>
       </c>
       <c r="I16" s="72" t="s">
         <v>319</v>
@@ -6698,7 +6698,7 @@
         <v>65</v>
       </c>
       <c r="H17" s="64" t="s">
-        <v>355</v>
+        <v>750</v>
       </c>
       <c r="I17" s="92" t="s">
         <v>319</v>
@@ -6745,7 +6745,7 @@
         <v>25</v>
       </c>
       <c r="C19" s="61" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D19" s="8">
         <v>2</v>
@@ -6904,7 +6904,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="77" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H24" s="57" t="s">
         <v>387</v>
@@ -6966,7 +6966,7 @@
         <v>1</v>
       </c>
       <c r="G26" s="77" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H26" s="57" t="s">
         <v>388</v>
@@ -7117,7 +7117,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="38" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H31" s="99" t="s">
         <v>391</v>
@@ -7237,7 +7237,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="97" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H35" s="58" t="s">
         <v>391</v>
@@ -7297,7 +7297,7 @@
         <v>1</v>
       </c>
       <c r="G37" s="97" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H37" s="99" t="s">
         <v>391</v>
@@ -7448,7 +7448,7 @@
         <v>1</v>
       </c>
       <c r="G42" s="97" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H42" s="99" t="s">
         <v>390</v>
@@ -7491,7 +7491,7 @@
         <v>409</v>
       </c>
       <c r="B44" s="81" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C44" s="62">
         <v>15</v>
@@ -7508,7 +7508,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="86" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H44" s="50" t="s">
         <v>392</v>
@@ -7522,7 +7522,7 @@
         <v>409</v>
       </c>
       <c r="B45" s="29" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C45" s="98">
         <v>14</v>
@@ -7539,13 +7539,13 @@
         <v>1</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H45" s="50" t="s">
         <v>392</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -7553,7 +7553,7 @@
         <v>409</v>
       </c>
       <c r="B46" s="29" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C46" s="98">
         <v>13</v>
@@ -7570,13 +7570,13 @@
         <v>1</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H46" s="50" t="s">
         <v>392</v>
       </c>
       <c r="I46" s="15" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -7584,7 +7584,7 @@
         <v>409</v>
       </c>
       <c r="B47" s="29" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C47" s="98">
         <v>12</v>
@@ -7601,13 +7601,13 @@
         <v>1</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H47" s="50" t="s">
         <v>392</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -7615,7 +7615,7 @@
         <v>409</v>
       </c>
       <c r="B48" s="29" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C48" s="98">
         <v>11</v>
@@ -7632,13 +7632,13 @@
         <v>1</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H48" s="50" t="s">
         <v>392</v>
       </c>
       <c r="I48" s="15" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -7646,7 +7646,7 @@
         <v>409</v>
       </c>
       <c r="B49" s="29" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C49" s="98">
         <v>10</v>
@@ -7663,13 +7663,13 @@
         <v>1</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H49" s="50" t="s">
         <v>392</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -7677,7 +7677,7 @@
         <v>409</v>
       </c>
       <c r="B50" s="29" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C50" s="98">
         <v>9</v>
@@ -7694,13 +7694,13 @@
         <v>1</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H50" s="50" t="s">
         <v>392</v>
       </c>
       <c r="I50" s="15" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -7708,7 +7708,7 @@
         <v>409</v>
       </c>
       <c r="B51" s="29" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C51" s="98">
         <v>8</v>
@@ -7725,13 +7725,13 @@
         <v>1</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H51" s="50" t="s">
         <v>392</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -7739,7 +7739,7 @@
         <v>409</v>
       </c>
       <c r="B52" s="29" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C52" s="98">
         <v>7</v>
@@ -7756,13 +7756,13 @@
         <v>1</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H52" s="50" t="s">
         <v>392</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -7770,7 +7770,7 @@
         <v>409</v>
       </c>
       <c r="B53" s="29" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C53" s="98">
         <v>6</v>
@@ -7787,13 +7787,13 @@
         <v>1</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H53" s="50" t="s">
         <v>392</v>
       </c>
       <c r="I53" s="15" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -7801,7 +7801,7 @@
         <v>409</v>
       </c>
       <c r="B54" s="29" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C54" s="98">
         <v>5</v>
@@ -7818,13 +7818,13 @@
         <v>1</v>
       </c>
       <c r="G54" s="19" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H54" s="50" t="s">
         <v>392</v>
       </c>
       <c r="I54" s="15" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -7832,7 +7832,7 @@
         <v>409</v>
       </c>
       <c r="B55" s="29" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C55" s="98">
         <v>4</v>
@@ -7849,13 +7849,13 @@
         <v>1</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H55" s="50" t="s">
         <v>392</v>
       </c>
       <c r="I55" s="15" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -7863,7 +7863,7 @@
         <v>409</v>
       </c>
       <c r="B56" s="29" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C56" s="98">
         <v>3</v>
@@ -7880,13 +7880,13 @@
         <v>1</v>
       </c>
       <c r="G56" s="19" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H56" s="50" t="s">
         <v>392</v>
       </c>
       <c r="I56" s="15" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -7894,7 +7894,7 @@
         <v>409</v>
       </c>
       <c r="B57" s="29" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C57" s="98">
         <v>2</v>
@@ -7911,13 +7911,13 @@
         <v>1</v>
       </c>
       <c r="G57" s="19" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H57" s="50" t="s">
         <v>392</v>
       </c>
       <c r="I57" s="15" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -7925,7 +7925,7 @@
         <v>409</v>
       </c>
       <c r="B58" s="29" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C58" s="98">
         <v>1</v>
@@ -7942,13 +7942,13 @@
         <v>1</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H58" s="50" t="s">
         <v>392</v>
       </c>
       <c r="I58" s="15" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -7956,7 +7956,7 @@
         <v>409</v>
       </c>
       <c r="B59" s="82" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C59" s="62">
         <v>0</v>
@@ -7973,7 +7973,7 @@
         <v>1</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H59" s="99" t="s">
         <v>392</v>
@@ -8007,7 +8007,7 @@
         <v>25</v>
       </c>
       <c r="H60" s="148" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="I60" s="149" t="s">
         <v>364</v>
@@ -8015,10 +8015,10 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="117" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B61" s="29" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C61" s="62">
         <v>7</v>
@@ -8035,10 +8035,10 @@
         <v>1</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H61" s="57" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="I61" s="19" t="s">
         <v>364</v>
@@ -8046,10 +8046,10 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="117" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B62" s="29" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C62" s="62">
         <v>6</v>
@@ -8066,10 +8066,10 @@
         <v>1</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H62" s="57" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="I62" s="19" t="s">
         <v>364</v>
@@ -8077,10 +8077,10 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="117" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B63" s="29" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C63" s="62">
         <v>5</v>
@@ -8097,10 +8097,10 @@
         <v>1</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H63" s="57" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="I63" s="19" t="s">
         <v>364</v>
@@ -8108,10 +8108,10 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="117" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B64" s="29" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C64" s="62">
         <v>4</v>
@@ -8128,10 +8128,10 @@
         <v>1</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H64" s="57" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="I64" s="19" t="s">
         <v>364</v>
@@ -8139,10 +8139,10 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="117" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B65" s="29" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C65" s="62">
         <v>3</v>
@@ -8159,10 +8159,10 @@
         <v>1</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H65" s="57" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="I65" s="19" t="s">
         <v>364</v>
@@ -8170,10 +8170,10 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="117" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B66" s="29" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C66" s="62">
         <v>2</v>
@@ -8190,10 +8190,10 @@
         <v>1</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H66" s="57" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="I66" s="19" t="s">
         <v>364</v>
@@ -8201,10 +8201,10 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="117" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B67" s="29" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C67" s="62">
         <v>1</v>
@@ -8221,10 +8221,10 @@
         <v>1</v>
       </c>
       <c r="G67" s="19" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H67" s="57" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="I67" s="19" t="s">
         <v>364</v>
@@ -8235,7 +8235,7 @@
         <v>328</v>
       </c>
       <c r="B68" s="147" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C68" s="93">
         <v>0</v>
@@ -8252,7 +8252,7 @@
         <v>1</v>
       </c>
       <c r="G68" s="46" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H68" s="99" t="s">
         <v>392</v>
@@ -8286,7 +8286,7 @@
         <v>25</v>
       </c>
       <c r="H69" s="57" t="s">
-        <v>393</v>
+        <v>752</v>
       </c>
       <c r="I69" s="15" t="s">
         <v>365</v>
@@ -8297,7 +8297,7 @@
         <v>329</v>
       </c>
       <c r="B70" s="28" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C70" s="98">
         <v>7</v>
@@ -8314,10 +8314,10 @@
         <v>1</v>
       </c>
       <c r="G70" s="19" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H70" s="57" t="s">
-        <v>393</v>
+        <v>752</v>
       </c>
       <c r="I70" s="15" t="s">
         <v>365</v>
@@ -8328,7 +8328,7 @@
         <v>329</v>
       </c>
       <c r="B71" s="29" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C71" s="98">
         <v>6</v>
@@ -8345,10 +8345,10 @@
         <v>1</v>
       </c>
       <c r="G71" s="84" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H71" s="57" t="s">
-        <v>393</v>
+        <v>752</v>
       </c>
       <c r="I71" s="15" t="s">
         <v>365</v>
@@ -8359,7 +8359,7 @@
         <v>329</v>
       </c>
       <c r="B72" s="28" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C72" s="98">
         <v>5</v>
@@ -8376,10 +8376,10 @@
         <v>1</v>
       </c>
       <c r="G72" s="88" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H72" s="57" t="s">
-        <v>393</v>
+        <v>752</v>
       </c>
       <c r="I72" s="15" t="s">
         <v>365</v>
@@ -8390,7 +8390,7 @@
         <v>329</v>
       </c>
       <c r="B73" s="29" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C73" s="98">
         <v>4</v>
@@ -8407,10 +8407,10 @@
         <v>1</v>
       </c>
       <c r="G73" s="88" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H73" s="57" t="s">
-        <v>393</v>
+        <v>752</v>
       </c>
       <c r="I73" s="15" t="s">
         <v>365</v>
@@ -8421,7 +8421,7 @@
         <v>329</v>
       </c>
       <c r="B74" s="29" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C74" s="98">
         <v>3</v>
@@ -8438,10 +8438,10 @@
         <v>1</v>
       </c>
       <c r="G74" s="88" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H74" s="57" t="s">
-        <v>393</v>
+        <v>752</v>
       </c>
       <c r="I74" s="15" t="s">
         <v>365</v>
@@ -8452,7 +8452,7 @@
         <v>329</v>
       </c>
       <c r="B75" s="29" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C75" s="98">
         <v>2</v>
@@ -8469,10 +8469,10 @@
         <v>1</v>
       </c>
       <c r="G75" s="88" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H75" s="57" t="s">
-        <v>393</v>
+        <v>752</v>
       </c>
       <c r="I75" s="15" t="s">
         <v>365</v>
@@ -8483,7 +8483,7 @@
         <v>329</v>
       </c>
       <c r="B76" s="160" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C76" s="62">
         <v>1</v>
@@ -8503,7 +8503,7 @@
         <v>90</v>
       </c>
       <c r="H76" s="57" t="s">
-        <v>393</v>
+        <v>752</v>
       </c>
       <c r="I76" s="15" t="s">
         <v>365</v>
@@ -8514,7 +8514,7 @@
         <v>329</v>
       </c>
       <c r="B77" s="80" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C77" s="93">
         <v>0</v>
@@ -8534,7 +8534,7 @@
         <v>89</v>
       </c>
       <c r="H77" s="99" t="s">
-        <v>393</v>
+        <v>752</v>
       </c>
       <c r="I77" s="41" t="s">
         <v>365</v>
@@ -8574,7 +8574,7 @@
         <v>331</v>
       </c>
       <c r="B79" s="43" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C79" s="62">
         <v>15</v>
@@ -8591,10 +8591,10 @@
         <v>1</v>
       </c>
       <c r="G79" s="86" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H79" s="50" t="s">
-        <v>393</v>
+        <v>752</v>
       </c>
       <c r="I79" s="15" t="s">
         <v>367</v>
@@ -8625,7 +8625,7 @@
         <v>92</v>
       </c>
       <c r="H80" s="57" t="s">
-        <v>393</v>
+        <v>752</v>
       </c>
       <c r="I80" s="15" t="s">
         <v>367</v>
@@ -8656,7 +8656,7 @@
         <v>94</v>
       </c>
       <c r="H81" s="57" t="s">
-        <v>393</v>
+        <v>752</v>
       </c>
       <c r="I81" s="15" t="s">
         <v>367</v>
@@ -8686,7 +8686,9 @@
       <c r="G82" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="H82" s="57"/>
+      <c r="H82" s="57" t="s">
+        <v>752</v>
+      </c>
       <c r="I82" s="15" t="s">
         <v>367</v>
       </c>
@@ -8716,7 +8718,7 @@
         <v>96</v>
       </c>
       <c r="H83" s="99" t="s">
-        <v>393</v>
+        <v>752</v>
       </c>
       <c r="I83" s="41" t="s">
         <v>367</v>
@@ -8747,7 +8749,7 @@
         <v>98</v>
       </c>
       <c r="H84" s="49" t="s">
-        <v>393</v>
+        <v>752</v>
       </c>
       <c r="I84" s="42" t="s">
         <v>368</v>
@@ -8808,7 +8810,9 @@
       <c r="G86" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="H86" s="57"/>
+      <c r="H86" s="57" t="s">
+        <v>751</v>
+      </c>
       <c r="I86" s="15" t="s">
         <v>369</v>
       </c>
@@ -8957,7 +8961,7 @@
         <v>1</v>
       </c>
       <c r="G91" s="19" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H91" s="57" t="s">
         <v>386</v>
@@ -9019,7 +9023,7 @@
         <v>1</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H93" s="57" t="s">
         <v>386</v>
@@ -9081,7 +9085,7 @@
         <v>1</v>
       </c>
       <c r="G95" s="19" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H95" s="57" t="s">
         <v>386</v>
@@ -9143,7 +9147,7 @@
         <v>1</v>
       </c>
       <c r="G97" s="19" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H97" s="57" t="s">
         <v>386</v>
@@ -9205,7 +9209,7 @@
         <v>1</v>
       </c>
       <c r="G99" s="19" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H99" s="57" t="s">
         <v>386</v>
@@ -9298,7 +9302,7 @@
         <v>1</v>
       </c>
       <c r="G102" s="19" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H102" s="57" t="s">
         <v>386</v>
@@ -9360,7 +9364,7 @@
         <v>1</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H104" s="57" t="s">
         <v>386</v>
@@ -9422,7 +9426,7 @@
         <v>1</v>
       </c>
       <c r="G106" s="19" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H106" s="57" t="s">
         <v>386</v>
@@ -9484,7 +9488,7 @@
         <v>1</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H108" s="57" t="s">
         <v>386</v>
@@ -9546,7 +9550,7 @@
         <v>1</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H110" s="57" t="s">
         <v>386</v>
@@ -9641,7 +9645,9 @@
       <c r="G113" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="H113" s="57"/>
+      <c r="H113" s="57" t="s">
+        <v>386</v>
+      </c>
       <c r="I113" s="15" t="s">
         <v>373</v>
       </c>
@@ -9668,7 +9674,7 @@
         <v>1</v>
       </c>
       <c r="G114" s="19" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H114" s="57" t="s">
         <v>386</v>
@@ -9730,7 +9736,7 @@
         <v>1</v>
       </c>
       <c r="G116" s="19" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H116" s="57" t="s">
         <v>386</v>
@@ -9761,7 +9767,7 @@
         <v>1</v>
       </c>
       <c r="G117" s="19" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H117" s="57" t="s">
         <v>386</v>
@@ -9823,7 +9829,7 @@
         <v>1</v>
       </c>
       <c r="G119" s="19" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H119" s="57" t="s">
         <v>386</v>
@@ -9885,7 +9891,7 @@
         <v>1</v>
       </c>
       <c r="G121" s="46" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H121" s="99" t="s">
         <v>386</v>
@@ -9899,7 +9905,7 @@
         <v>414</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C122" s="62">
         <v>15</v>
@@ -9916,10 +9922,10 @@
         <v>1</v>
       </c>
       <c r="G122" s="15" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H122" s="50" t="s">
-        <v>393</v>
+        <v>752</v>
       </c>
       <c r="I122" s="15" t="s">
         <v>374</v>
@@ -9950,7 +9956,7 @@
         <v>153</v>
       </c>
       <c r="H123" s="57" t="s">
-        <v>393</v>
+        <v>752</v>
       </c>
       <c r="I123" s="15" t="s">
         <v>374</v>
@@ -9981,7 +9987,7 @@
         <v>155</v>
       </c>
       <c r="H124" s="57" t="s">
-        <v>393</v>
+        <v>752</v>
       </c>
       <c r="I124" s="15" t="s">
         <v>374</v>
@@ -10011,7 +10017,9 @@
       <c r="G125" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="H125" s="57"/>
+      <c r="H125" s="57" t="s">
+        <v>752</v>
+      </c>
       <c r="I125" s="15" t="s">
         <v>374</v>
       </c>
@@ -10041,7 +10049,7 @@
         <v>157</v>
       </c>
       <c r="H126" s="99" t="s">
-        <v>393</v>
+        <v>752</v>
       </c>
       <c r="I126" s="46" t="s">
         <v>374</v>
@@ -10072,7 +10080,7 @@
         <v>159</v>
       </c>
       <c r="H127" s="49" t="s">
-        <v>393</v>
+        <v>752</v>
       </c>
       <c r="I127" s="42" t="s">
         <v>375</v>
@@ -10083,7 +10091,7 @@
         <v>416</v>
       </c>
       <c r="B128" s="40" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C128" s="65" t="s">
         <v>311</v>
@@ -10100,10 +10108,10 @@
         <v>1</v>
       </c>
       <c r="G128" s="42" t="s">
+        <v>566</v>
+      </c>
+      <c r="H128" s="49" t="s">
         <v>567</v>
-      </c>
-      <c r="H128" s="49" t="s">
-        <v>568</v>
       </c>
       <c r="I128" s="42" t="s">
         <v>376</v>
@@ -10134,7 +10142,7 @@
         <v>26</v>
       </c>
       <c r="H129" s="49" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I129" s="42" t="s">
         <v>377</v>
@@ -10282,7 +10290,7 @@
         <v>1</v>
       </c>
       <c r="G134" s="46" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H134" s="99" t="s">
         <v>391</v>
@@ -10433,7 +10441,7 @@
         <v>1</v>
       </c>
       <c r="G139" s="46" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H139" s="99" t="s">
         <v>391</v>
@@ -10584,7 +10592,7 @@
         <v>1</v>
       </c>
       <c r="G144" s="46" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H144" s="99" t="s">
         <v>391</v>
@@ -10703,7 +10711,7 @@
         <v>306</v>
       </c>
       <c r="B1" s="110" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C1" s="110" t="s">
         <v>308</v>
@@ -10732,7 +10740,7 @@
         <v>420</v>
       </c>
       <c r="B2" s="155" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C2" s="65" t="s">
         <v>311</v>
@@ -10749,10 +10757,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="138" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2" s="155" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="I2" s="138"/>
     </row>
@@ -10761,7 +10769,7 @@
         <v>421</v>
       </c>
       <c r="B3" s="155" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C3" s="65" t="s">
         <v>311</v>
@@ -10778,10 +10786,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="138" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H3" s="155" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="I3" s="138"/>
     </row>
@@ -10790,7 +10798,7 @@
         <v>422</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C4" s="50">
         <v>0</v>
@@ -10811,7 +10819,7 @@
       </c>
       <c r="H4" s="50"/>
       <c r="I4" s="50" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -10836,13 +10844,13 @@
         <v>1</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="I5" s="57" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10867,13 +10875,13 @@
         <v>1</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>174</v>
       </c>
       <c r="I6" s="57" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10898,13 +10906,13 @@
         <v>1</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>174</v>
       </c>
       <c r="I7" s="57" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -10929,13 +10937,13 @@
         <v>1</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>174</v>
       </c>
       <c r="I8" s="57" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10960,13 +10968,13 @@
         <v>1</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>174</v>
       </c>
       <c r="I9" s="57" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10991,13 +10999,13 @@
         <v>1</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>179</v>
       </c>
       <c r="I10" s="57" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -11005,7 +11013,7 @@
         <v>422</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C11" s="57">
         <v>9</v>
@@ -11022,13 +11030,13 @@
         <v>1</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>180</v>
       </c>
       <c r="I11" s="57" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -11053,13 +11061,13 @@
         <v>1</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>182</v>
       </c>
       <c r="I12" s="57" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -11084,13 +11092,13 @@
         <v>1</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>182</v>
       </c>
       <c r="I13" s="57" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -11115,13 +11123,13 @@
         <v>1</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>174</v>
       </c>
       <c r="I14" s="57" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -11146,13 +11154,13 @@
         <v>1</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>174</v>
       </c>
       <c r="I15" s="57" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -11181,7 +11189,7 @@
       </c>
       <c r="H16" s="57"/>
       <c r="I16" s="57" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -11210,7 +11218,7 @@
       </c>
       <c r="H17" s="99"/>
       <c r="I17" s="99" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -11235,13 +11243,13 @@
         <v>1</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="I18" s="57" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -11266,13 +11274,13 @@
         <v>1</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>188</v>
       </c>
       <c r="I19" s="57" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="75" x14ac:dyDescent="0.25">
@@ -11297,13 +11305,13 @@
         <v>1</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="I20" s="57" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -11328,13 +11336,13 @@
         <v>1</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>192</v>
       </c>
       <c r="I21" s="57" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -11359,13 +11367,13 @@
         <v>1</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>194</v>
       </c>
       <c r="I22" s="57" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -11390,13 +11398,13 @@
         <v>1</v>
       </c>
       <c r="G23" s="16" t="s">
+        <v>680</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>681</v>
       </c>
-      <c r="H23" s="5" t="s">
-        <v>682</v>
-      </c>
       <c r="I23" s="57" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -11421,13 +11429,13 @@
         <v>1</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="I24" s="57" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="90" x14ac:dyDescent="0.25">
@@ -11452,13 +11460,13 @@
         <v>1</v>
       </c>
       <c r="G25" s="16" t="s">
+        <v>683</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>684</v>
       </c>
-      <c r="H25" s="5" t="s">
-        <v>685</v>
-      </c>
       <c r="I25" s="57" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -11483,13 +11491,13 @@
         <v>1</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="I26" s="57" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="120" x14ac:dyDescent="0.25">
@@ -11514,13 +11522,13 @@
         <v>1</v>
       </c>
       <c r="G27" s="16" t="s">
+        <v>686</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>687</v>
       </c>
-      <c r="H27" s="5" t="s">
-        <v>688</v>
-      </c>
       <c r="I27" s="57" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="165" x14ac:dyDescent="0.25">
@@ -11545,13 +11553,13 @@
         <v>1</v>
       </c>
       <c r="G28" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>689</v>
       </c>
-      <c r="H28" s="5" t="s">
-        <v>690</v>
-      </c>
       <c r="I28" s="57" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -11576,13 +11584,13 @@
         <v>1</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="I29" s="57" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -11593,7 +11601,7 @@
         <v>202</v>
       </c>
       <c r="C30" s="94" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D30" s="57">
         <v>2</v>
@@ -11607,13 +11615,13 @@
         <v>1</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>203</v>
       </c>
       <c r="I30" s="57" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -11621,7 +11629,7 @@
         <v>423</v>
       </c>
       <c r="B31" s="99" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C31" s="99">
         <v>15</v>
@@ -11638,13 +11646,13 @@
         <v>1</v>
       </c>
       <c r="G31" s="64" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H31" s="109" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="I31" s="99" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -11652,7 +11660,7 @@
         <v>424</v>
       </c>
       <c r="B32" s="49" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C32" s="65" t="s">
         <v>311</v>
@@ -11669,7 +11677,7 @@
         <v>1</v>
       </c>
       <c r="G32" s="139" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H32" s="49"/>
       <c r="I32" s="49"/>
@@ -11679,7 +11687,7 @@
         <v>425</v>
       </c>
       <c r="B33" s="49" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C33" s="65" t="s">
         <v>311</v>
@@ -11696,7 +11704,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="139" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H33" s="49"/>
       <c r="I33" s="49"/>
@@ -11706,7 +11714,7 @@
         <v>426</v>
       </c>
       <c r="B34" s="49" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C34" s="65" t="s">
         <v>311</v>
@@ -11723,7 +11731,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="139" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H34" s="49"/>
       <c r="I34" s="49"/>
@@ -11733,7 +11741,7 @@
         <v>427</v>
       </c>
       <c r="B35" s="49" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C35" s="65" t="s">
         <v>311</v>
@@ -11750,7 +11758,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="139" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H35" s="49"/>
       <c r="I35" s="49"/>
@@ -11760,7 +11768,7 @@
         <v>428</v>
       </c>
       <c r="B36" s="49" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C36" s="65" t="s">
         <v>311</v>
@@ -11777,7 +11785,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="139" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H36" s="49"/>
       <c r="I36" s="49"/>
@@ -11787,7 +11795,7 @@
         <v>429</v>
       </c>
       <c r="B37" s="49" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C37" s="65" t="s">
         <v>311</v>
@@ -11804,17 +11812,17 @@
         <v>1</v>
       </c>
       <c r="G37" s="139" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H37" s="49"/>
       <c r="I37" s="49"/>
     </row>
     <row r="38" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="144" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B38" s="49" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C38" s="65" t="s">
         <v>311</v>
@@ -11831,17 +11839,17 @@
         <v>1</v>
       </c>
       <c r="G38" s="139" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H38" s="49"/>
       <c r="I38" s="49"/>
     </row>
     <row r="39" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="144" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B39" s="49" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C39" s="65" t="s">
         <v>311</v>
@@ -11858,17 +11866,17 @@
         <v>1</v>
       </c>
       <c r="G39" s="139" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H39" s="49"/>
       <c r="I39" s="49"/>
     </row>
     <row r="40" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="144" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B40" s="49" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C40" s="65" t="s">
         <v>311</v>
@@ -11885,17 +11893,17 @@
         <v>1</v>
       </c>
       <c r="G40" s="139" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H40" s="49"/>
       <c r="I40" s="49"/>
     </row>
     <row r="41" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="144" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B41" s="49" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C41" s="65" t="s">
         <v>311</v>
@@ -11912,20 +11920,20 @@
         <v>1</v>
       </c>
       <c r="G41" s="139" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H41" s="49"/>
       <c r="I41" s="49"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="118" t="s">
+        <v>568</v>
+      </c>
+      <c r="B42" s="130" t="s">
         <v>569</v>
       </c>
-      <c r="B42" s="130" t="s">
-        <v>570</v>
-      </c>
       <c r="C42" s="115" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D42" s="130">
         <v>15</v>
@@ -11939,17 +11947,17 @@
         <v>1</v>
       </c>
       <c r="G42" s="131" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H42" s="132"/>
       <c r="I42" s="130"/>
     </row>
     <row r="43" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="119" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B43" s="133" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C43" s="133">
         <v>0</v>
@@ -11966,17 +11974,17 @@
         <v>1</v>
       </c>
       <c r="G43" s="134" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H43" s="135"/>
       <c r="I43" s="133"/>
     </row>
     <row r="44" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="111" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B44" s="127" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C44" s="94" t="s">
         <v>311</v>
@@ -11993,7 +12001,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="128" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H44" s="129"/>
       <c r="I44" s="127"/>
@@ -12062,7 +12070,7 @@
         <v>306</v>
       </c>
       <c r="B1" s="110" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C1" s="110" t="s">
         <v>308</v>
@@ -12108,11 +12116,11 @@
         <v>1</v>
       </c>
       <c r="G2" s="99" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H2" s="64"/>
       <c r="I2" s="99" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -12143,7 +12151,7 @@
         <v>206</v>
       </c>
       <c r="I3" s="50" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -12168,11 +12176,11 @@
         <v>1</v>
       </c>
       <c r="G4" s="57" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H4" s="16"/>
       <c r="I4" s="57" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -12197,13 +12205,13 @@
         <v>1</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H5" s="16" t="s">
         <v>215</v>
       </c>
       <c r="I5" s="57" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="110.25" x14ac:dyDescent="0.25">
@@ -12228,13 +12236,13 @@
         <v>1</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="I6" s="57" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -12259,13 +12267,13 @@
         <v>1</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H7" s="16" t="s">
         <v>215</v>
       </c>
       <c r="I7" s="57" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -12296,7 +12304,7 @@
         <v>215</v>
       </c>
       <c r="I8" s="57" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -12324,10 +12332,10 @@
         <v>213</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="I9" s="57" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -12352,11 +12360,11 @@
         <v>1</v>
       </c>
       <c r="G10" s="57" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H10" s="16"/>
       <c r="I10" s="57" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -12381,11 +12389,11 @@
         <v>1</v>
       </c>
       <c r="G11" s="57" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H11" s="16"/>
       <c r="I11" s="57" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -12413,10 +12421,10 @@
         <v>190</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="I12" s="57" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -12424,10 +12432,10 @@
         <v>431</v>
       </c>
       <c r="B13" s="57" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C13" s="105" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D13" s="57">
         <v>2</v>
@@ -12441,11 +12449,11 @@
         <v>1</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H13" s="16"/>
       <c r="I13" s="57" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -12470,13 +12478,13 @@
         <v>1</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="I14" s="57" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -12501,13 +12509,13 @@
         <v>1</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H15" s="16" t="s">
         <v>215</v>
       </c>
       <c r="I15" s="57" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -12536,7 +12544,7 @@
       </c>
       <c r="H16" s="16"/>
       <c r="I16" s="57" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -12561,11 +12569,11 @@
         <v>1</v>
       </c>
       <c r="G17" s="99" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H17" s="64"/>
       <c r="I17" s="99" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -12590,13 +12598,13 @@
         <v>1</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="I18" s="50" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
@@ -12621,13 +12629,13 @@
         <v>1</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="I19" s="57" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -12638,7 +12646,7 @@
         <v>26</v>
       </c>
       <c r="C20" s="105" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D20" s="57">
         <v>5</v>
@@ -12652,11 +12660,11 @@
         <v>1</v>
       </c>
       <c r="G20" s="57" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H20" s="16"/>
       <c r="I20" s="57" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -12664,10 +12672,10 @@
         <v>432</v>
       </c>
       <c r="B21" s="57" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C21" s="105" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D21" s="57">
         <v>2</v>
@@ -12687,7 +12695,7 @@
         <v>215</v>
       </c>
       <c r="I21" s="57" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -12698,7 +12706,7 @@
         <v>26</v>
       </c>
       <c r="C22" s="105" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D22" s="57">
         <v>2</v>
@@ -12712,11 +12720,11 @@
         <v>1</v>
       </c>
       <c r="G22" s="57" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H22" s="16"/>
       <c r="I22" s="57" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="63" x14ac:dyDescent="0.25">
@@ -12741,13 +12749,13 @@
         <v>1</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="I23" s="57" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -12755,7 +12763,7 @@
         <v>432</v>
       </c>
       <c r="B24" s="57" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C24" s="57">
         <v>12</v>
@@ -12776,7 +12784,7 @@
       </c>
       <c r="H24" s="16"/>
       <c r="I24" s="57" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12787,7 +12795,7 @@
         <v>240</v>
       </c>
       <c r="C25" s="106" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D25" s="99">
         <v>3</v>
@@ -12801,13 +12809,13 @@
         <v>1</v>
       </c>
       <c r="G25" s="64" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H25" s="64" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="I25" s="99" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -12832,13 +12840,13 @@
         <v>1</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="I26" s="50" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -12849,7 +12857,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="105" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D27" s="57">
         <v>2</v>
@@ -12863,11 +12871,11 @@
         <v>1</v>
       </c>
       <c r="G27" s="57" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H27" s="16"/>
       <c r="I27" s="57" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -12878,7 +12886,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="105" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D28" s="57">
         <v>3</v>
@@ -12892,11 +12900,11 @@
         <v>1</v>
       </c>
       <c r="G28" s="57" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H28" s="16"/>
       <c r="I28" s="57" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -12921,11 +12929,11 @@
         <v>1</v>
       </c>
       <c r="G29" s="57" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H29" s="16"/>
       <c r="I29" s="57" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -12936,7 +12944,7 @@
         <v>242</v>
       </c>
       <c r="C30" s="105" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D30" s="57">
         <v>2</v>
@@ -12950,13 +12958,13 @@
         <v>1</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="I30" s="57" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="126" x14ac:dyDescent="0.25">
@@ -12981,13 +12989,13 @@
         <v>1</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="I31" s="57" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -13012,11 +13020,11 @@
         <v>1</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H32" s="16"/>
       <c r="I32" s="57" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="110.25" x14ac:dyDescent="0.25">
@@ -13041,13 +13049,13 @@
         <v>1</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="I33" s="57" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="126" x14ac:dyDescent="0.25">
@@ -13072,13 +13080,13 @@
         <v>1</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="I34" s="57" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -13103,13 +13111,13 @@
         <v>1</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="I35" s="57" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13120,7 +13128,7 @@
         <v>26</v>
       </c>
       <c r="C36" s="106" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D36" s="99">
         <v>2</v>
@@ -13134,11 +13142,11 @@
         <v>1</v>
       </c>
       <c r="G36" s="99" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H36" s="64"/>
       <c r="I36" s="99" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -13149,7 +13157,7 @@
         <v>26</v>
       </c>
       <c r="C37" s="107" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D37" s="50">
         <v>3</v>
@@ -13163,11 +13171,11 @@
         <v>1</v>
       </c>
       <c r="G37" s="108" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H37" s="8"/>
       <c r="I37" s="57" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -13192,11 +13200,11 @@
         <v>1</v>
       </c>
       <c r="G38" s="57" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H38" s="16"/>
       <c r="I38" s="57" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -13207,7 +13215,7 @@
         <v>26</v>
       </c>
       <c r="C39" s="105" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D39" s="57">
         <v>2</v>
@@ -13221,11 +13229,11 @@
         <v>1</v>
       </c>
       <c r="G39" s="57" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H39" s="16"/>
       <c r="I39" s="57" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -13250,11 +13258,11 @@
         <v>1</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H40" s="16"/>
       <c r="I40" s="57" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -13283,7 +13291,7 @@
       </c>
       <c r="H41" s="16"/>
       <c r="I41" s="57" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -13312,7 +13320,7 @@
       </c>
       <c r="H42" s="16"/>
       <c r="I42" s="57" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -13341,7 +13349,7 @@
       </c>
       <c r="H43" s="16"/>
       <c r="I43" s="57" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -13366,11 +13374,11 @@
         <v>1</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H44" s="16"/>
       <c r="I44" s="57" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -13399,7 +13407,7 @@
       </c>
       <c r="H45" s="16"/>
       <c r="I45" s="57" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13410,7 +13418,7 @@
         <v>26</v>
       </c>
       <c r="C46" s="106" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D46" s="99">
         <v>4</v>
@@ -13424,11 +13432,11 @@
         <v>1</v>
       </c>
       <c r="G46" s="99" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H46" s="64"/>
       <c r="I46" s="99" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13453,11 +13461,11 @@
         <v>1</v>
       </c>
       <c r="G47" s="49" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H47" s="66"/>
       <c r="I47" s="99" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -13482,11 +13490,11 @@
         <v>1</v>
       </c>
       <c r="G48" s="50" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H48" s="8"/>
       <c r="I48" s="57" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -13511,11 +13519,11 @@
         <v>1</v>
       </c>
       <c r="G49" s="57" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H49" s="16"/>
       <c r="I49" s="57" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -13540,11 +13548,11 @@
         <v>1</v>
       </c>
       <c r="G50" s="57" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H50" s="16"/>
       <c r="I50" s="57" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -13569,11 +13577,11 @@
         <v>1</v>
       </c>
       <c r="G51" s="57" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H51" s="16"/>
       <c r="I51" s="57" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -13598,11 +13606,11 @@
         <v>1</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H52" s="16"/>
       <c r="I52" s="57" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -13627,11 +13635,11 @@
         <v>1</v>
       </c>
       <c r="G53" s="57" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H53" s="16"/>
       <c r="I53" s="57" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -13656,11 +13664,11 @@
         <v>1</v>
       </c>
       <c r="G54" s="57" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H54" s="16"/>
       <c r="I54" s="57" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -13689,7 +13697,7 @@
       </c>
       <c r="H55" s="16"/>
       <c r="I55" s="57" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -13718,7 +13726,7 @@
       </c>
       <c r="H56" s="16"/>
       <c r="I56" s="57" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -13747,7 +13755,7 @@
       </c>
       <c r="H57" s="16"/>
       <c r="I57" s="57" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -13776,7 +13784,7 @@
       </c>
       <c r="H58" s="16"/>
       <c r="I58" s="57" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -13805,7 +13813,7 @@
       </c>
       <c r="H59" s="16"/>
       <c r="I59" s="57" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -13834,7 +13842,7 @@
       </c>
       <c r="H60" s="16"/>
       <c r="I60" s="57" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -13863,7 +13871,7 @@
       </c>
       <c r="H61" s="16"/>
       <c r="I61" s="57" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -13892,7 +13900,7 @@
       </c>
       <c r="H62" s="16"/>
       <c r="I62" s="57" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13917,11 +13925,11 @@
         <v>1</v>
       </c>
       <c r="G63" s="99" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H63" s="64"/>
       <c r="I63" s="99" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13946,11 +13954,11 @@
         <v>1</v>
       </c>
       <c r="G64" s="49" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H64" s="66"/>
       <c r="I64" s="49" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
@@ -13958,7 +13966,7 @@
         <v>438</v>
       </c>
       <c r="B65" s="58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C65" s="90" t="s">
         <v>311</v>
@@ -13975,7 +13983,7 @@
         <v>1</v>
       </c>
       <c r="G65" s="91" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H65" s="91"/>
       <c r="I65" s="58"/>
@@ -13985,7 +13993,7 @@
         <v>439</v>
       </c>
       <c r="B66" s="58" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C66" s="90" t="s">
         <v>311</v>
@@ -14002,17 +14010,17 @@
         <v>1</v>
       </c>
       <c r="G66" s="91" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H66" s="91"/>
       <c r="I66" s="58"/>
     </row>
     <row r="67" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="111" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B67" s="58" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C67" s="90" t="s">
         <v>311</v>
@@ -14029,17 +14037,17 @@
         <v>1</v>
       </c>
       <c r="G67" s="91" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H67" s="91"/>
       <c r="I67" s="58"/>
     </row>
     <row r="68" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="111" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B68" s="58" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C68" s="90" t="s">
         <v>311</v>
@@ -14056,17 +14064,17 @@
         <v>1</v>
       </c>
       <c r="G68" s="91" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H68" s="91"/>
       <c r="I68" s="58"/>
     </row>
     <row r="69" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="111" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B69" s="58" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C69" s="90" t="s">
         <v>311</v>
@@ -14083,17 +14091,17 @@
         <v>1</v>
       </c>
       <c r="G69" s="91" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H69" s="91"/>
       <c r="I69" s="58"/>
     </row>
     <row r="70" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="111" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B70" s="58" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C70" s="90" t="s">
         <v>311</v>
@@ -14110,17 +14118,17 @@
         <v>1</v>
       </c>
       <c r="G70" s="91" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H70" s="91"/>
       <c r="I70" s="58"/>
     </row>
     <row r="71" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="111" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B71" s="58" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C71" s="90" t="s">
         <v>311</v>
@@ -14137,17 +14145,17 @@
         <v>1</v>
       </c>
       <c r="G71" s="91" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H71" s="91"/>
       <c r="I71" s="58"/>
     </row>
     <row r="72" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="111" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B72" s="58" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C72" s="90" t="s">
         <v>311</v>
@@ -14164,7 +14172,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="91" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H72" s="91"/>
       <c r="I72" s="58"/>
@@ -14221,7 +14229,7 @@
         <v>306</v>
       </c>
       <c r="B1" s="110" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C1" s="110" t="s">
         <v>308</v>
@@ -14244,13 +14252,13 @@
     </row>
     <row r="2" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="156" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B2" s="157" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C2" s="158" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D2" s="66">
         <v>5120</v>
@@ -14264,19 +14272,19 @@
         <v>320</v>
       </c>
       <c r="G2" s="159" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H2" s="10"/>
     </row>
     <row r="3" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="156" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B3" s="157" t="s">
+        <v>630</v>
+      </c>
+      <c r="C3" s="158" t="s">
         <v>631</v>
-      </c>
-      <c r="C3" s="158" t="s">
-        <v>632</v>
       </c>
       <c r="D3" s="66">
         <v>5120</v>
@@ -14290,19 +14298,19 @@
         <v>320</v>
       </c>
       <c r="G3" s="159" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H3" s="150"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="156" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B4" s="165" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="158" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D4" s="66">
         <v>37888</v>
@@ -14316,7 +14324,7 @@
         <v>2368</v>
       </c>
       <c r="G4" s="159" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H4" s="150"/>
     </row>
@@ -14394,7 +14402,7 @@
         <v>306</v>
       </c>
       <c r="B1" s="110" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C1" s="110" t="s">
         <v>308</v>
@@ -14437,7 +14445,7 @@
         <v>2</v>
       </c>
       <c r="G2" s="108" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H2" s="21" t="s">
         <v>258</v>
@@ -14466,7 +14474,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="108" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H3" s="21" t="s">
         <v>258</v>
@@ -14495,7 +14503,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="108" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H4" s="21" t="s">
         <v>258</v>
@@ -14524,7 +14532,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="108" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H5" s="21" t="s">
         <v>258</v>
@@ -14553,7 +14561,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="108" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H6" s="21" t="s">
         <v>258</v>
@@ -14582,7 +14590,7 @@
         <v>2</v>
       </c>
       <c r="G7" s="108" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H7" s="21" t="s">
         <v>258</v>
@@ -14611,7 +14619,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="108" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H8" s="21" t="s">
         <v>258</v>
@@ -14640,7 +14648,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="108" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H9" s="21" t="s">
         <v>258</v>
@@ -14669,7 +14677,7 @@
         <v>2</v>
       </c>
       <c r="G10" s="108" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H10" s="21" t="s">
         <v>258</v>
@@ -14698,7 +14706,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="108" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H11" s="21" t="s">
         <v>258</v>
@@ -14727,7 +14735,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="108" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H12" s="21" t="s">
         <v>258</v>
@@ -14756,7 +14764,7 @@
         <v>2</v>
       </c>
       <c r="G13" s="108" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H13" s="21" t="s">
         <v>258</v>
@@ -14785,7 +14793,7 @@
         <v>2</v>
       </c>
       <c r="G14" s="108" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H14" s="21" t="s">
         <v>258</v>
@@ -14814,7 +14822,7 @@
         <v>2</v>
       </c>
       <c r="G15" s="108" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H15" s="21" t="s">
         <v>258</v>
@@ -14843,7 +14851,7 @@
         <v>2</v>
       </c>
       <c r="G16" s="108" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H16" s="21" t="s">
         <v>258</v>
@@ -14872,7 +14880,7 @@
         <v>2</v>
       </c>
       <c r="G17" s="108" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H17" s="16" t="s">
         <v>258</v>
@@ -14884,7 +14892,7 @@
         <v>1020</v>
       </c>
       <c r="B18" s="57" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C18" s="94" t="s">
         <v>307</v>
@@ -14901,7 +14909,7 @@
         <v>2</v>
       </c>
       <c r="G18" s="108" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H18" s="16" t="s">
         <v>258</v>
@@ -14913,7 +14921,7 @@
         <v>1022</v>
       </c>
       <c r="B19" s="57" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C19" s="94" t="s">
         <v>307</v>
@@ -14930,7 +14938,7 @@
         <v>2</v>
       </c>
       <c r="G19" s="108" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H19" s="16" t="s">
         <v>258</v>
@@ -14942,7 +14950,7 @@
         <v>1024</v>
       </c>
       <c r="B20" s="57" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C20" s="94" t="s">
         <v>307</v>
@@ -14959,7 +14967,7 @@
         <v>2</v>
       </c>
       <c r="G20" s="108" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H20" s="16" t="s">
         <v>258</v>
@@ -14971,7 +14979,7 @@
         <v>1026</v>
       </c>
       <c r="B21" s="57" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C21" s="94" t="s">
         <v>307</v>
@@ -14988,7 +14996,7 @@
         <v>2</v>
       </c>
       <c r="G21" s="108" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H21" s="16" t="s">
         <v>258</v>
@@ -15000,10 +15008,10 @@
         <v>1028</v>
       </c>
       <c r="B22" s="99" t="s">
+        <v>553</v>
+      </c>
+      <c r="C22" s="95" t="s">
         <v>554</v>
-      </c>
-      <c r="C22" s="95" t="s">
-        <v>555</v>
       </c>
       <c r="D22" s="99">
         <v>1920</v>
@@ -15032,7 +15040,7 @@
         <v>276</v>
       </c>
       <c r="C23" s="61" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D23" s="50">
         <v>384</v>
@@ -15046,7 +15054,7 @@
         <v>24</v>
       </c>
       <c r="G23" s="108" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H23" s="50" t="s">
         <v>275</v>
@@ -15061,7 +15069,7 @@
         <v>277</v>
       </c>
       <c r="C24" s="94" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D24" s="57">
         <v>384</v>
@@ -15075,7 +15083,7 @@
         <v>24</v>
       </c>
       <c r="G24" s="108" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H24" s="57" t="s">
         <v>275</v>
@@ -15090,7 +15098,7 @@
         <v>278</v>
       </c>
       <c r="C25" s="94" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D25" s="57">
         <v>384</v>
@@ -15104,7 +15112,7 @@
         <v>24</v>
       </c>
       <c r="G25" s="108" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H25" s="57" t="s">
         <v>275</v>
@@ -15119,7 +15127,7 @@
         <v>279</v>
       </c>
       <c r="C26" s="94" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D26" s="57">
         <v>384</v>
@@ -15133,7 +15141,7 @@
         <v>24</v>
       </c>
       <c r="G26" s="108" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H26" s="57" t="s">
         <v>275</v>
@@ -15148,7 +15156,7 @@
         <v>280</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D27" s="57">
         <v>384</v>
@@ -15162,7 +15170,7 @@
         <v>24</v>
       </c>
       <c r="G27" s="108" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H27" s="57" t="s">
         <v>275</v>
@@ -15177,7 +15185,7 @@
         <v>281</v>
       </c>
       <c r="C28" s="94" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D28" s="57">
         <v>384</v>
@@ -15191,7 +15199,7 @@
         <v>24</v>
       </c>
       <c r="G28" s="108" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H28" s="57" t="s">
         <v>275</v>
@@ -15206,7 +15214,7 @@
         <v>282</v>
       </c>
       <c r="C29" s="94" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D29" s="57">
         <v>384</v>
@@ -15220,7 +15228,7 @@
         <v>24</v>
       </c>
       <c r="G29" s="108" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H29" s="57" t="s">
         <v>275</v>
@@ -15235,7 +15243,7 @@
         <v>283</v>
       </c>
       <c r="C30" s="94" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D30" s="57">
         <v>384</v>
@@ -15249,7 +15257,7 @@
         <v>24</v>
       </c>
       <c r="G30" s="108" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H30" s="57" t="s">
         <v>275</v>
@@ -15264,7 +15272,7 @@
         <v>284</v>
       </c>
       <c r="C31" s="94" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D31" s="57">
         <v>384</v>
@@ -15278,7 +15286,7 @@
         <v>24</v>
       </c>
       <c r="G31" s="108" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H31" s="57" t="s">
         <v>275</v>
@@ -15293,7 +15301,7 @@
         <v>285</v>
       </c>
       <c r="C32" s="94" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D32" s="57">
         <v>384</v>
@@ -15307,7 +15315,7 @@
         <v>24</v>
       </c>
       <c r="G32" s="108" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H32" s="57" t="s">
         <v>275</v>
@@ -15322,7 +15330,7 @@
         <v>286</v>
       </c>
       <c r="C33" s="94" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D33" s="57">
         <v>384</v>
@@ -15336,7 +15344,7 @@
         <v>24</v>
       </c>
       <c r="G33" s="108" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H33" s="57" t="s">
         <v>275</v>
@@ -15351,7 +15359,7 @@
         <v>287</v>
       </c>
       <c r="C34" s="94" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D34" s="57">
         <v>384</v>
@@ -15365,7 +15373,7 @@
         <v>24</v>
       </c>
       <c r="G34" s="108" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H34" s="57" t="s">
         <v>275</v>
@@ -15380,7 +15388,7 @@
         <v>288</v>
       </c>
       <c r="C35" s="94" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D35" s="57">
         <v>384</v>
@@ -15394,7 +15402,7 @@
         <v>24</v>
       </c>
       <c r="G35" s="108" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H35" s="57" t="s">
         <v>275</v>
@@ -15409,7 +15417,7 @@
         <v>289</v>
       </c>
       <c r="C36" s="94" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D36" s="57">
         <v>384</v>
@@ -15423,7 +15431,7 @@
         <v>24</v>
       </c>
       <c r="G36" s="108" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H36" s="57" t="s">
         <v>275</v>
@@ -15438,7 +15446,7 @@
         <v>290</v>
       </c>
       <c r="C37" s="94" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D37" s="57">
         <v>384</v>
@@ -15452,7 +15460,7 @@
         <v>24</v>
       </c>
       <c r="G37" s="108" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H37" s="57" t="s">
         <v>275</v>
@@ -15467,7 +15475,7 @@
         <v>291</v>
       </c>
       <c r="C38" s="94" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D38" s="57">
         <v>384</v>
@@ -15481,7 +15489,7 @@
         <v>24</v>
       </c>
       <c r="G38" s="108" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H38" s="57" t="s">
         <v>275</v>
@@ -15493,10 +15501,10 @@
         <v>1220</v>
       </c>
       <c r="B39" s="57" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C39" s="94" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D39" s="57">
         <v>256</v>
@@ -15510,7 +15518,7 @@
         <v>16</v>
       </c>
       <c r="G39" s="57" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H39" s="57" t="s">
         <v>275</v>
@@ -15522,10 +15530,10 @@
         <v>1230</v>
       </c>
       <c r="B40" s="57" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C40" s="94" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D40" s="57">
         <v>256</v>
@@ -15539,7 +15547,7 @@
         <v>16</v>
       </c>
       <c r="G40" s="57" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H40" s="57" t="s">
         <v>275</v>
@@ -15551,10 +15559,10 @@
         <v>1240</v>
       </c>
       <c r="B41" s="57" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C41" s="94" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D41" s="57">
         <v>256</v>
@@ -15568,7 +15576,7 @@
         <v>16</v>
       </c>
       <c r="G41" s="57" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H41" s="57" t="s">
         <v>275</v>
@@ -15580,10 +15588,10 @@
         <v>1250</v>
       </c>
       <c r="B42" s="57" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C42" s="94" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D42" s="57">
         <v>256</v>
@@ -15597,7 +15605,7 @@
         <v>16</v>
       </c>
       <c r="G42" s="57" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H42" s="57" t="s">
         <v>275</v>
@@ -15612,7 +15620,7 @@
         <v>25</v>
       </c>
       <c r="C43" s="94" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D43" s="57">
         <v>39424</v>
@@ -15681,36 +15689,36 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="110" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B1" s="110" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="110" t="s">
+        <v>711</v>
+      </c>
+      <c r="D1" s="110" t="s">
         <v>712</v>
       </c>
-      <c r="D1" s="110" t="s">
+      <c r="E1" s="110" t="s">
         <v>713</v>
       </c>
-      <c r="E1" s="110" t="s">
+      <c r="F1" s="110" t="s">
         <v>714</v>
       </c>
-      <c r="F1" s="110" t="s">
+      <c r="G1" s="110" t="s">
         <v>715</v>
       </c>
-      <c r="G1" s="110" t="s">
-        <v>716</v>
-      </c>
       <c r="H1" s="110" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="51" t="s">
+        <v>716</v>
+      </c>
+      <c r="B2" s="16" t="s">
         <v>717</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>718</v>
       </c>
       <c r="C2" s="16">
         <v>0</v>
@@ -15727,7 +15735,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H2" s="18" t="s">
         <v>296</v>
@@ -15742,7 +15750,7 @@
         <v>26</v>
       </c>
       <c r="C3" s="115" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D3" s="21">
         <v>15</v>
@@ -15756,7 +15764,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H3" s="21"/>
     </row>
@@ -15783,10 +15791,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -15798,7 +15806,7 @@
         <v>26</v>
       </c>
       <c r="C5" s="115" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D5" s="21">
         <v>15</v>
@@ -15812,7 +15820,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H5" s="21"/>
     </row>
@@ -15822,10 +15830,10 @@
         <v>1C02</v>
       </c>
       <c r="B6" s="16" t="s">
+        <v>721</v>
+      </c>
+      <c r="C6" s="115" t="s">
         <v>722</v>
-      </c>
-      <c r="C6" s="115" t="s">
-        <v>723</v>
       </c>
       <c r="D6" s="16">
         <v>256</v>
@@ -15839,10 +15847,10 @@
         <v>16</v>
       </c>
       <c r="G6" s="16" t="s">
+        <v>723</v>
+      </c>
+      <c r="H6" s="16" t="s">
         <v>724</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.25">
@@ -15854,7 +15862,7 @@
         <v>295</v>
       </c>
       <c r="C7" s="115" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D7" s="18">
         <v>384</v>
@@ -15868,7 +15876,7 @@
         <v>24</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H7" s="16" t="s">
         <v>296</v>
@@ -15883,7 +15891,7 @@
         <v>297</v>
       </c>
       <c r="C8" s="115" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D8" s="18">
         <v>768</v>
@@ -15897,10 +15905,10 @@
         <v>48</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -15912,7 +15920,7 @@
         <v>298</v>
       </c>
       <c r="C9" s="115" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D9" s="18">
         <v>128</v>
@@ -15926,10 +15934,10 @@
         <v>8</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="87.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -15938,10 +15946,10 @@
         <v>1C62</v>
       </c>
       <c r="B10" s="154" t="s">
+        <v>728</v>
+      </c>
+      <c r="C10" s="115" t="s">
         <v>729</v>
-      </c>
-      <c r="C10" s="115" t="s">
-        <v>730</v>
       </c>
       <c r="D10" s="18">
         <v>8192</v>
@@ -15955,10 +15963,10 @@
         <v>512</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -15970,7 +15978,7 @@
         <v>299</v>
       </c>
       <c r="C11" s="115" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D11" s="18">
         <v>768</v>
@@ -15984,10 +15992,10 @@
         <v>48</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -15999,7 +16007,7 @@
         <v>26</v>
       </c>
       <c r="C12" s="115" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D12" s="21">
         <v>3808</v>
@@ -16013,7 +16021,7 @@
         <v>238</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H12" s="21"/>
     </row>
@@ -16047,7 +16055,7 @@
         <v>380</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8">
@@ -16065,10 +16073,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
+        <v>734</v>
+      </c>
+      <c r="B15" s="16" t="s">
         <v>735</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>736</v>
       </c>
     </row>
   </sheetData>
@@ -16079,34 +16087,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="0358a91d-8923-4300-9035-92feb74d70aa">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <MediaLengthInSeconds xmlns="94916c3f-a887-466e-9071-419f2f5fc067" xsi:nil="true"/>
-    <TaxCatchAll xmlns="0358a91d-8923-4300-9035-92feb74d70aa" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="94916c3f-a887-466e-9071-419f2f5fc067">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FB031FF8E1109D43B2BDF0F43F684A4E" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b896ebdbfa452e7a07541eac816e2062">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="94916c3f-a887-466e-9071-419f2f5fc067" xmlns:ns3="0358a91d-8923-4300-9035-92feb74d70aa" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="556acc82b7336cf142ff4903a3ab7ecb" ns2:_="" ns3:_="">
     <xsd:import namespace="94916c3f-a887-466e-9071-419f2f5fc067"/>
@@ -16361,7 +16341,54 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="0358a91d-8923-4300-9035-92feb74d70aa">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <MediaLengthInSeconds xmlns="94916c3f-a887-466e-9071-419f2f5fc067" xsi:nil="true"/>
+    <TaxCatchAll xmlns="0358a91d-8923-4300-9035-92feb74d70aa" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="94916c3f-a887-466e-9071-419f2f5fc067">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15AAF0E9-722A-46AD-84E0-1D9BE67AFFE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="94916c3f-a887-466e-9071-419f2f5fc067"/>
+    <ds:schemaRef ds:uri="0358a91d-8923-4300-9035-92feb74d70aa"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58344122-BFEB-4801-99ED-3DACB961442B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -16378,29 +16405,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06808489-AD29-49EF-A920-5725306266D8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15AAF0E9-722A-46AD-84E0-1D9BE67AFFE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="94916c3f-a887-466e-9071-419f2f5fc067"/>
-    <ds:schemaRef ds:uri="0358a91d-8923-4300-9035-92feb74d70aa"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>